--- a/InputFiles/ICDC/TC08_ICDC_COTC022_Sex-Female.xlsx
+++ b/InputFiles/ICDC/TC08_ICDC_COTC022_Sex-Female.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10802"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/epishinavv/git/Commons_Automation/InputFiles/ICDC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52327F59-86FC-BA46-B3DC-A4729C5F7626}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98EA014A-99B6-E646-9E2F-A3B8BBFF42A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="40100" yWindow="1360" windowWidth="16700" windowHeight="12640" xr2:uid="{8362173B-D28C-47E7-8626-98E16101E601}"/>
+    <workbookView xWindow="67900" yWindow="4980" windowWidth="29500" windowHeight="14700" xr2:uid="{8362173B-D28C-47E7-8626-98E16101E601}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -271,6 +271,7 @@
          WHEN cf.file_name LIKE '%.fastq.gz' THEN 'fastq'
         WHEN cf.file_name LIKE '%.vcf.gz' THEN 'vcf'
         WHEN cf.file_name LIKE '%.tsv.gz' THEN 'tsv'
+        WHEN cf.file_name LIKE '%.txt.gz' THEN 'txt'
         WHEN cf.file_name LIKE '%.pdf' THEN 'pdf'
         WHEN cf.file_name LIKE '%.rtf' THEN 'rtf'
         WHEN cf.file_name LIKE '%.tbi' THEN 'tbi'
